--- a/stories/arbres/ATOM-VIV.ANI.001-01.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Léa marche avec papa. Ils visitent la ferme. Un chien arrive. Le chien aboie. Ouaf ouaf. Papa dit : le chien aboie. Un chat saute. Le chat miaule. Miaou. Une vache mange. La vache meugle. Meuh. Un coq est sur le mur. Le coq chante. Cocorico. Un canard nage. Le canard cancane. Papa dit : chaque animal a un cri. Léa nomme l'animal. Elle dit le cri.</t>
+          <t>Léa marche avec papa. Ils visitent la ferme. Un chien arrive. Le chien aboie. Ouaf ouaf. Le chien aboie. Un chat saute. Le chat miaule. Miaou. Une vache mange. La vache meugle. Meuh. Un coq est sur le mur. Le coq chante. Cocorico. Un canard nage. Le canard cancane. Chaque animal a un cri. Léa nomme l'animal. Elle dit le cri.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Léa marche avec papa. Ils visitent la ferme. Un chien arrive. Le chien aboie. Ouaf ouaf.
+papa|Le chien aboie.
+narrateur|Un chat saute. Le chat miaule. Miaou. Une vache mange. La vache meugle. Meuh. Un coq est sur le mur. Le coq chante. Cocorico. Un canard nage. Le canard cancane.
+papa|Chaque animal a un cri.
+narrateur|Léa nomme l'animal. Elle dit le cri.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le chien fait ouaf. Quel est son cri ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a nommé l'animal. Elle a dit le cri. Chien, chat, vache, coq, canard.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1834,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Léa tient la main de papa. La ferme sent le foin.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2001,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2041,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.001-01.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.001-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Léa nomme l'animal. Elle dit le cri.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1509,11 @@
       <c r="AW3" t="inlineStr">
         <is>
           <t>narrateur|Le chien fait ouaf. Quel est son cri ?</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -1672,6 +1687,11 @@
           <t>narrateur|Léa a nommé l'animal. Elle a dit le cri. Chien, chat, vache, coq, canard.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1839,6 +1859,7 @@
           <t>narrateur|Léa tient la main de papa. La ferme sent le foin.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2006,6 +2027,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2024,7 +2046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2048,6 +2070,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2249,6 +2285,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-VIV.ANI.001-01.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Les cris de la ferme</t>
+          <t>Le silence du coq</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Aniss veut entendre le coq. Le coq se tait. Une poule caquette. Puis le coq chante. Aniss a son cri.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Léa marche avec papa. Ils visitent la ferme. Un chien arrive. Le chien aboie. Ouaf ouaf. Le chien aboie. Un chat saute. Le chat miaule. Miaou. Une vache mange. La vache meugle. Meuh. Un coq est sur le mur. Le coq chante. Cocorico. Un canard nage. Le canard cancane. Chaque animal a un cri. Léa nomme l'animal. Elle dit le cri.</t>
+          <t>Le foin pique les chaussures d'Aniss. La cour sent le bois chaud. Une barrière craque un peu. Tu entends, Aniss ? Pas encore. Je veux le coq. Le coq du mur ? Oui. Son chant. Ils marchent dans la paille. Ça croustille sous les pieds. En ce moment, Aniss lève les yeux. Le coq est sur le mur. Il a des plumes rousses. Il ne chante pas. Il se tait. On attend ? Oui, papa. Une poule arrive près du seau. Elle caquette. Cot cot cot. Ce n'est pas lui. C'est la poule. Elle parle d'abord. Aniss serre la main de papa. Le seau tremble un peu. L'eau fait un cercle. Le coq tourne la tête. Il reste muet. Pourquoi ? Il cherche son moment. Tu restes ? Je reste. La poule picore près des pieds. Ses plumes sont chaudes de soleil. Aniss ne bouge presque pas. Tu es patient. J'écoute. Un silence tient la cour. Le foin sent plus fort. Puis le coq gonfle le cou. Il chante. Cocorico. Le voilà ! Tu l'as entendu. Merci d'avoir attendu. Encore ? On écoute encore ? Oui. Le coq se tait une seconde. Puis il reprend. Cocorico. C'est son cri. Oui. Le cri du coq. La poule caquette plus bas. Elle n'est plus la première. Tu voulais le coq. Je l'ai. Une plume rousse tombe près du seau. Aniss la regarde, sans la prendre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Léa marche avec papa. Ils visitent la ferme. Un chien arrive. Le chien aboie. Ouaf ouaf. Papa dit : le chien aboie. Un chat saute. Le chat miaule. Miaou. Une vache mange. La vache meugle. Meuh. Un coq est sur le mur. Le coq chante. Cocorico. Un canard nage. Le canard cancane. Papa dit : chaque animal a un cri. Léa &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt;me l'animal. Elle dit le cri.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le foin pique les chaussures d'Aniss. La cour sent le bois chaud. Une barrière craque un peu. Tu entends, Aniss ? Pas encore. Je veux le coq. Le coq du mur ? Oui. Son chant. Ils marchent dans la paille. Ça croustille sous les pieds. En ce moment, Aniss lève les yeux. Le coq est sur le mur. Il a des plumes rousses. Il ne chante pas. Il se tait. On attend ? Oui, papa. Une poule arrive près du seau. Elle caquette. Cot cot cot. Ce n'est pas lui. C'est la poule. Elle parle d'abord. Aniss serre la main de papa. Le seau tremble un peu. L'eau fait un cercle. Le coq tourne la tête. Il reste muet. Pourquoi ? Il cherche son moment. Tu restes ? Je reste. La poule picore près des pieds. Ses plumes sont chaudes de soleil. Aniss ne bouge presque pas. Tu es patient. J'écoute. Un silence tient la cour. Le foin sent plus fort. Puis le coq gonfle le cou. Il chante. Cocorico. Le voilà ! Tu l'as entendu. Merci d'avoir attendu. Encore ? On écoute encore ? Oui. Le coq se tait une seconde. Puis il reprend. Cocorico. C'est son cri. Oui. Le cri du coq. La poule caquette plus bas. Elle n'est plus la première. Tu voulais le coq. Je l'ai. Une plume rousse tombe près du seau. Aniss la regarde, sans la prendre.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,11 +1324,67 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Léa marche avec papa. Ils visitent la ferme. Un chien arrive. Le chien aboie. Ouaf ouaf.
-papa|Le chien aboie.
-narrateur|Un chat saute. Le chat miaule. Miaou. Une vache mange. La vache meugle. Meuh. Un coq est sur le mur. Le coq chante. Cocorico. Un canard nage. Le canard cancane.
-papa|Chaque animal a un cri.
-narrateur|Léa nomme l'animal. Elle dit le cri.</t>
+          <t>narrateur|Le foin pique les chaussures d'Aniss.
+narrateur|La cour sent le bois chaud.
+narrateur|Une barrière craque un peu.
+papa|Tu entends, Aniss ?
+enfant-m|Pas encore.
+enfant-m|Je veux le coq.
+papa|Le coq du mur ?
+enfant-m|Oui.
+enfant-m|Son chant.
+narrateur|Ils marchent dans la paille.
+narrateur|Ça croustille sous les pieds.
+narrateur|En ce moment, Aniss lève les yeux.
+narrateur|Le coq est sur le mur.
+narrateur|Il a des plumes rousses.
+narrateur|Il ne chante pas.
+enfant-m|Il se tait.
+papa|On attend ?
+enfant-m|Oui, papa.
+narrateur|Une poule arrive près du seau.
+narrateur|Elle caquette.
+narrateur|Cot cot cot.
+enfant-m|Ce n'est pas lui.
+papa|C'est la poule.
+papa|Elle parle d'abord.
+narrateur|Aniss serre la main de papa.
+narrateur|Le seau tremble un peu.
+narrateur|L'eau fait un cercle.
+narrateur|Le coq tourne la tête.
+narrateur|Il reste muet.
+enfant-m|Pourquoi ?
+papa|Il cherche son moment.
+papa|Tu restes ?
+enfant-m|Je reste.
+narrateur|La poule picore près des pieds.
+narrateur|Ses plumes sont chaudes de soleil.
+narrateur|Aniss ne bouge presque pas.
+papa|Tu es patient.
+enfant-m|J'écoute.
+narrateur|Un silence tient la cour.
+narrateur|Le foin sent plus fort.
+narrateur|Puis le coq gonfle le cou.
+narrateur|Il chante.
+narrateur|Cocorico.
+enfant-m|Le voilà !
+papa|Tu l'as entendu.
+papa|Merci d'avoir attendu.
+enfant-m|Encore ?
+papa|On écoute encore ?
+enfant-m|Oui.
+narrateur|Le coq se tait une seconde.
+narrateur|Puis il reprend.
+narrateur|Cocorico.
+enfant-m|C'est son cri.
+papa|Oui.
+papa|Le cri du coq.
+narrateur|La poule caquette plus bas.
+narrateur|Elle n'est plus la première.
+papa|Tu voulais le coq.
+enfant-m|Je l'ai.
+narrateur|Une plume rousse tombe près du seau.
+narrateur|Aniss la regarde, sans la prendre.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1348,12 +1416,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le chien fait ouaf. Quel est son cri ?</t>
+          <t>Quel est le cri du coq ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le chien fait ouaf. Quel est son &lt;emphasis level="moderate"&gt;cri&lt;/emphasis&gt; ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Quel est le cri du coq ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1363,12 +1431,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>aboie</t>
+          <t>cocorico</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>aboie | il aboie | ouaf | le cri</t>
+          <t>cocorico | il chante | coq | le coq | chante | son cri</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1383,7 +1451,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Le chien aboie. Quel est le cri ?</t>
+          <t>Le coq chante cocorico. Quel est son cri ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1432,7 +1500,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1508,7 +1576,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le chien fait ouaf. Quel est son cri ?</t>
+          <t>narrateur|Quel est le cri du coq ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1540,12 +1608,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Léa a nommé l'animal. Elle a dit le cri. Chien, chat, vache, coq, canard.</t>
+          <t>Aniss lève encore le menton. Cocorico. Oui. Le coq chante cocorico. Bravo. La poule, cot cot. La poule d'abord. Puis le coq. Le mur de pierre est chaud. Les plumes rousses brillent. Tu as attendu. Il s'était tu. Puis il a parlé. Tu l'entends encore ? Un peu. Un dernier cocorico part vers le champ. Il s'amincit, puis plus rien. Il a chanté pour toi.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Léa a &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt;mé l'animal. Elle a dit le cri. Chien, chat, vache, coq, canard.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss lève encore le menton. Cocorico. Oui. Le coq chante cocorico. Bravo. La poule, cot cot. La poule d'abord. Puis le coq. Le mur de pierre est chaud. Les plumes rousses brillent. Tu as attendu. Il s'était tu. Puis il a parlé. Tu l'entends encore ? Un peu. Un dernier cocorico part vers le champ. Il s'amincit, puis plus rien. Il a chanté pour toi.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1601,14 +1669,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1684,7 +1752,24 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Léa a nommé l'animal. Elle a dit le cri. Chien, chat, vache, coq, canard.</t>
+          <t>narrateur|Aniss lève encore le menton.
+enfant-m|Cocorico.
+papa|Oui.
+papa|Le coq chante cocorico.
+papa|Bravo.
+enfant-m|La poule, cot cot.
+papa|La poule d'abord.
+papa|Puis le coq.
+narrateur|Le mur de pierre est chaud.
+narrateur|Les plumes rousses brillent.
+papa|Tu as attendu.
+enfant-m|Il s'était tu.
+papa|Puis il a parlé.
+papa|Tu l'entends encore ?
+enfant-m|Un peu.
+narrateur|Un dernier cocorico part vers le champ.
+narrateur|Il s'amincit, puis plus rien.
+papa|Il a chanté pour toi.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1716,12 +1801,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Léa tient la main de papa. La ferme sent le foin.</t>
+          <t>Ils redescendent la cour. Le foin pique encore. J'ai son cri. Cocorico. Cocorico. La poule suit un moment. Puis elle s'arrête au seau. Elle reste ici. Le coq aussi. Sur le mur. Aniss se retourne. Le coq est une tache rousse. Tu veux la plume ? Oui. Il la prend, toute légère. Merci d'avoir écouté. La plume chatouille sa paume. La cour sent le bois et l'eau.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Léa tient la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; de papa. La ferme sent le foin.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Ils redescendent la cour. Le foin pique encore. J'ai son cri. Cocorico. Cocorico. La poule suit un moment. Puis elle s'arrête au seau. Elle reste ici. Le coq aussi. Sur le mur. Aniss se retourne. Le coq est une tache rousse. Tu veux la plume ? Oui. Il la prend, toute légère. Merci d'avoir écouté. La plume chatouille sa paume. La cour sent le bois et l'eau.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1777,14 +1862,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1856,10 +1941,26 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Léa tient la main de papa. La ferme sent le foin.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Ils redescendent la cour.
+narrateur|Le foin pique encore.
+enfant-m|J'ai son cri.
+papa|Cocorico.
+enfant-m|Cocorico.
+narrateur|La poule suit un moment.
+narrateur|Puis elle s'arrête au seau.
+papa|Elle reste ici.
+enfant-m|Le coq aussi.
+papa|Sur le mur.
+narrateur|Aniss se retourne.
+narrateur|Le coq est une tache rousse.
+papa|Tu veux la plume ?
+enfant-m|Oui.
+narrateur|Il la prend, toute légère.
+papa|Merci d'avoir écouté.
+narrateur|La plume chatouille sa paume.
+narrateur|La cour sent le bois et l'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1884,12 +1985,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le coq a chanté. Tu l'as entendu. La plume rousse tremble dans la main. Un peu de foin reste sur la chaussure. Le mur garde encore le soleil du coq.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le coq a chanté. Tu l'as entendu. La plume rousse tremble dans la main. Un peu de foin reste sur la chaussure. Le mur garde encore le soleil du coq.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1945,14 +2046,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2024,10 +2125,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-m|Le coq a chanté.
+papa|Tu l'as entendu.
+narrateur|La plume rousse tremble dans la main.
+narrateur|Un peu de foin reste sur la chaussure.
+narrateur|Le mur garde encore le soleil du coq.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2046,7 +2150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2084,6 +2188,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.001-01.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.001-01.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ferme</t>
+          <t>cour de ferme, foin, mur de pierre</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Léa, papa</t>
+          <t>Aniss, papa</t>
         </is>
       </c>
     </row>
